--- a/human_resources_forms/021_reference_check_for_team_members--human_resources_forms.xlsx
+++ b/human_resources_forms/021_reference_check_for_team_members--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_sn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>What is the team member's job title?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_description_sn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>What is the team member's job description?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,64 +566,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>work_experience</t>
+          <t>work_experience_sn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Work Experience</t>
+          <t>How many years of work experience does the team member have?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>work_history</t>
+          <t>reference_1_available_sn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Work History</t>
+          <t>Is the reference 1 available for a call?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reference_1</t>
+          <t>reference_1_name_sn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reference 1</t>
+          <t>What is the name of the reference 1?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +635,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reference_1_name</t>
+          <t>reference_1_contact_sn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reference 1 Name</t>
+          <t>What is the contact information of the reference 1?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reference_1_contact</t>
+          <t>reference_2_available_sn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reference 1 Contact</t>
+          <t>Is the reference 2 available for a call?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reference_2</t>
+          <t>reference_2_name_sn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reference 2</t>
+          <t>What is the name of the reference 2?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reference_2_name</t>
+          <t>reference_2_contact_sn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reference 2 Name</t>
+          <t>What is the contact information of the reference 2?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reference_2_contact</t>
+          <t>performance_rating_sn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reference 2 Contact</t>
+          <t>What is the team member's performance rating?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>performance_rating</t>
+          <t>relationship_sn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>What is the relationship between the team member and the reference 1?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>relationship</t>
+          <t>experience_sn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>What is the team member's experience?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>evaluation_sn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>What is the evaluation of the team member?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>evaluation_frequency_sn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>What is the evaluation frequency of the team member?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,64 +842,64 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>evaluation_frequency</t>
+          <t>evaluation_basis_sn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Evaluation Frequency</t>
+          <t>What is the evaluation basis of the team member?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>evaluation_basis</t>
+          <t>reference_3_available_sn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evaluation Basis</t>
+          <t>Is the reference 3 available for a call?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>reference_3</t>
+          <t>reference_3_name_sn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reference 3</t>
+          <t>What is the name of the reference 3?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,64 +911,64 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>reference_3_name</t>
+          <t>reference_3_contact_sn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reference 3 Name</t>
+          <t>What is the contact information of the reference 3?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>reference_3_contact</t>
+          <t>performance_rating_2_sn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reference 3 Contact</t>
+          <t>Performance Rating 2 Sn</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>performance_rating_2</t>
+          <t>relationship_2_sn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>What is the relationship between the team member and the reference 2?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,18 +980,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>relationship_2</t>
+          <t>experience_2_sn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Experience 2 Sn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1003,18 +1003,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>experience_2</t>
+          <t>evaluation_2_sn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Evaluation 2 Sn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1026,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>evaluation_2</t>
+          <t>evaluation_frequency_2_sn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Evaluation Frequency 2 Sn</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1049,18 +1049,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>evaluation_frequency_2</t>
+          <t>evaluation_basis_2_sn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evaluation Frequency</t>
+          <t>Evaluation Basis 2 Sn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1072,18 +1072,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>evaluation_basis_2</t>
+          <t>final_note_sn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evaluation Basis</t>
+          <t>Is there any additional comments or notes that would be helpful to consider during the reference check?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,340 +1126,289 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_experience_choices</t>
+          <t>work_experience_sn_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'5_years'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '5 years'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>work_experience_choices</t>
+          <t>work_experience_sn_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3_years'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3 years'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>work_experience_choices</t>
+          <t>work_experience_sn_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'2_years'}</t>
+          <t>2_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '2 years'}</t>
+          <t>2 years</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>work_experience_choices</t>
+          <t>work_experience_sn_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'1_year'}</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '1 year'}</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>work_experience_choices</t>
+          <t>work_experience_sn_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'less_than_1_year'}</t>
+          <t>5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Less than 1 year'}</t>
+          <t>5 years</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reference_1_choices</t>
+          <t>reference_1_available_sn_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reference_1_choices</t>
+          <t>reference_1_available_sn_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reference_1_choices</t>
+          <t>reference_2_available_sn_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>reference_2_choices</t>
+          <t>reference_2_available_sn_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reference_2_choices</t>
+          <t>performance_rating_sn_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_available'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Available'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_2_choices</t>
+          <t>performance_rating_sn_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Available'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>performance_rating_choices</t>
+          <t>performance_rating_sn_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>performance_rating_choices</t>
+          <t>reference_3_available_sn_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'very_good'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Very Good'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>performance_rating_choices</t>
+          <t>reference_3_available_sn_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'needs_improvement'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Needs Improvement'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reference_3_choices</t>
+          <t>performance_rating_2_sn_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reference_3_choices</t>
+          <t>performance_rating_2_sn_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_available'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Available'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reference_3_choices</t>
+          <t>performance_rating_2_sn_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Available'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>performance_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>performance_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>performance_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'needs_improvement'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Needs Improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
